--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,198 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Plaid</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Fraud Data Partnerships</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco HQ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/plaid/4003dc3c-5714-4449-bf65-ac0c7d5385e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Plaid</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Data Scientist - Fraud</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New York City Office</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/plaid/361c4725-ab72-4895-a3aa-9b642f4927a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Plaid</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Data Science Manager - Fraud</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New York City Office</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/plaid/55eacfa6-71e0-42ac-8788-04dc1e5fd694</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Plaid</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer - Infra/Ops - Fraud</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New York City Office</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/plaid/e9a9aeab-be90-43f3-b898-63a846cb5777</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Plaid</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer (Research Scientist) - Fraud</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>New York City Office</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/plaid/5e56c0a6-3caa-4255-8c63-95c29cbc2a32</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Plaid</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer - Fraud</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>San Francisco HQ</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/plaid/85cd5d07-9920-45fa-931a-daf8c3558e5b</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3692,58 +3746,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,70 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Account Executive Product - Fraud &amp; Risk </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chicago, Seattle, NYC, San Francisco, Remote </t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8181024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Director, Global Trust &amp; Safety, Compliance &amp; Business Enablement</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New York, NY; San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8782314002?gh_jid=8782314002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,70 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Account Executive Product - Fraud &amp; Risk </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chicago, Seattle, NYC, San Francisco, Remote </t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8181024</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Lyft</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Director, Global Trust &amp; Safety, Compliance &amp; Business Enablement</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New York, NY; San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8782314002?gh_jid=8782314002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rover</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fraud Investigator II</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/rover/c817f2b8-a1dd-4a38-b2fc-b35390763cdd</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Rover</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Fraud Investigator II</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/rover/c817f2b8-a1dd-4a38-b2fc-b35390763cdd</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Manager, Safeguards (Account Integrity &amp; Abuse) </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards, Account Integrity</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5413576008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Product Manager, Safeguards (Account Integrity &amp; Abuse) </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards, Account Integrity</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5413576008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3564,58 +3618,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,70 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Manager, Safeguards (Generalist) </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5400720008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Product Policy Lead, Regulation </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/780b0dfa-1068-4e94-8dc9-84b7fd1c5264</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,12 +470,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product Manager, Safeguards (Generalist) </t>
+          <t>Program Manager, Safeguards Workforce Operations</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco, CA | New York City, NY</t>
+          <t>San Francisco, CA | Seattle, WA | New York City, NY | Washington, DC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -485,14 +485,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5400720008</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5431285008</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -502,22 +502,150 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Senior Product Policy Lead, Regulation </t>
+          <t>Abuse Investigator - Scams &amp; Fraud</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>US - Remote</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Product Policy</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/780b0dfa-1068-4e94-8dc9-84b7fd1c5264</t>
+          <t>https://jobs.ashbyhq.com/openai/7512a020-2f3c-4f19-921d-b76edaeba5d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fraud Investigator</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chicago, IL; Denver, CO; Westlake, TX</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8214553?t=gh_src=&amp;gh_jid=8214553</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chime</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Product Manager - Trust and Safety</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/chime/jobs/8831472002?gh_jid=8831472002</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Senior Advanced Analyst, Fraud &amp; Safety Investigations</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com/positions/8225785?gh_jid=8225785</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Senior Staff Fraud Strategy Analyst, Card</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TX - Frisco</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://sofi.com/careers/job/8002663003?gh_jid=8002663003</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,198 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Program Manager, Safeguards Workforce Operations</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | Seattle, WA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5431285008</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Abuse Investigator - Scams &amp; Fraud</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>US - Remote</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/openai/7512a020-2f3c-4f19-921d-b76edaeba5d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Robinhood</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fraud Investigator</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Chicago, IL; Denver, CO; Westlake, TX</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8214553?t=gh_src=&amp;gh_jid=8214553</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Product Manager - Trust and Safety</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8831472002?gh_jid=8831472002</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Airbnb</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Senior Advanced Analyst, Fraud &amp; Safety Investigations</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://careers.airbnb.com/positions/8225785?gh_jid=8225785</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Senior Staff Fraud Strategy Analyst, Card</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TX - Frisco</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://sofi.com/careers/job/8002663003?gh_jid=8002663003</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="53" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Product Designer, Safeguards</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5428014008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="53" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Product Designer, Safeguards</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5428014008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3724,58 +3778,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Program Manager, Safeguards Policy, Enforcement, and Threat Intelligence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5440535008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Program Manager, Safeguards Policy, Enforcement, and Threat Intelligence</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5440535008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,102 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Community Operations Specialist</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Community Operations</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8257185</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Staff Product Manager, Radar - Fraud and Abuse Prevention</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>San Francisco, Seattle, New York, US-Remote</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8258815</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sr. Manager, Ads Product Policy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US; Remote, US</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8222282</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="59" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,39 +460,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Community Operations Specialist</t>
+          <t xml:space="preserve">Communications Manager, Safeguards </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>San Francisco, CA | New York City, NY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Community Operations</t>
+          <t>Safeguards</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8257185</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5445577008</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Staff Product Manager, Radar - Fraud and Abuse Prevention</t>
+          <t>Fraud Architect</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>San Francisco, Seattle, New York, US-Remote</t>
+          <t>SF-HQ, Chicago, New York, US-Remote</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,39 +517,167 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8258815</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8203220</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Payments Fraud Investigator</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8261213</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sr. Manager, Ads Product Policy</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist, Trust and Safety</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>San Francisco, CA, US; Remote, US</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Product Policy</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8222282</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7987856</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Chime</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/chime/jobs/8875820002?gh_jid=8875820002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Chime</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Senior Staff / Staff Software Engineer, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/chime/jobs/8875914002?gh_jid=8875914002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chime</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/chime/jobs/8875663002?gh_jid=8875663002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,230 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Communications Manager, Safeguards </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5445577008</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Fraud Architect</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SF-HQ, Chicago, New York, US-Remote</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8203220</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Payments Fraud Investigator</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8261213</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Staff Data Scientist, Trust and Safety</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US; Remote, US</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7987856</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8875820002?gh_jid=8875820002</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Senior Staff / Staff Software Engineer, Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8875914002?gh_jid=8875914002</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Software Engineer, Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8875663002?gh_jid=8875663002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,70 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Staff+ Fullstack Software Engineer, Safeguards Engineering</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5369710008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Credit Risk, Fraud Strategist</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>South San Francisco</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8267684</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,70 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Staff+ Fullstack Software Engineer, Safeguards Engineering</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5369710008</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Credit Risk, Fraud Strategist</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>South San Francisco</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8267684</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3820,58 +3874,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Account Executive Product - Fraud &amp; Risk </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8271657</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Account Executive Product - Fraud &amp; Risk </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8271657</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="59" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,102 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Staff Community Product Marketing Manager, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8302227</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Senior Product Manager, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8900844002?gh_jid=8900844002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Senior Product Manager, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8889185002?gh_jid=8889185002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="59" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="59" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,96 +460,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Staff Community Product Marketing Manager, Trust &amp; Safety</t>
+          <t>Product Manager, Radar - Fraud and Abuse Prevention</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>San Francisco, Seattle, New York, US-Remote</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8302227</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8306158</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Senior Product Manager, Trust &amp; Safety</t>
+          <t>Fraud Strategy Associate</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>São Paulo, São Paulo, Brazil</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8900844002?gh_jid=8900844002</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lyft</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Senior Product Manager, Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8889185002?gh_jid=8889185002</t>
+          <t>https://www.brex.com/careers/8903752002?gh_jid=8903752002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="53" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="59" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,64 +460,256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Product Manager, Radar - Fraud and Abuse Prevention</t>
+          <t>Applied Scientist, Product Policy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco, Seattle, New York, US-Remote</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Product Policy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8306158</t>
+          <t>https://jobs.ashbyhq.com/openai/6ef9babb-e210-496f-a004-fed919a9ed2d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fraud Investigations Analyst</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Denver, CO; Westlake, TX</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8226972?t=gh_src=&amp;gh_jid=8226972</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fraud Operations Program Manager</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chicago, IL; Denver, CO; Lake Mary, FL; Westlake, TX</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8312485?t=gh_src=&amp;gh_jid=8312485</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Brex</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Fraud Strategy Associate</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>São Paulo, São Paulo, Brazil</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8903752002?gh_jid=8903752002</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.brex.com/careers/8907623002?gh_jid=8907623002</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fraud Strategy Associate</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Vancouver, British Columbia, Canada</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.brex.com/careers/8907499002?gh_jid=8907499002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fraud Strategy Associate</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Salt Lake City, Utah, United States</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.brex.com/careers/8907553002?gh_jid=8907553002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fraud Strategy Associate</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>San Francisco, California, United States</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.brex.com/careers/8907563002?gh_jid=8907563002</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fraud Strategy Associate</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.brex.com/careers/8907584002?gh_jid=8907584002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Applied Scientist, Product Policy</t>
+          <t>Product Policy Lead, Ads</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Francisco, CA, US; Remote, US</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -485,231 +485,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/6ef9babb-e210-496f-a004-fed919a9ed2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Robinhood</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Fraud Investigations Analyst</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Denver, CO; Westlake, TX</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8226972?t=gh_src=&amp;gh_jid=8226972</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Robinhood</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fraud Operations Program Manager</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Chicago, IL; Denver, CO; Lake Mary, FL; Westlake, TX</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8312485?t=gh_src=&amp;gh_jid=8312485</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Fraud Strategy Associate</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8907623002?gh_jid=8907623002</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fraud Strategy Associate</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Vancouver, British Columbia, Canada</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8907499002?gh_jid=8907499002</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Fraud Strategy Associate</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Salt Lake City, Utah, United States</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8907553002?gh_jid=8907553002</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Fraud Strategy Associate</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>San Francisco, California, United States</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8907563002?gh_jid=8907563002</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Fraud Strategy Associate</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>New York, New York, United States</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8907584002?gh_jid=8907584002</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8287196</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -419,10 +419,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,32 +460,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Product Policy Lead, Ads</t>
+          <t>Incident Manager, Safeguards</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US; Remote, US</t>
+          <t>San Francisco, CA | New York City, NY | Washington, DC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Product Policy</t>
+          <t>Safeguards</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8287196</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5462881008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Incident Manager, Safeguards</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5462881008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3916,58 +3970,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sales Manager, Product- Fraud &amp; Risk</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dublin or London</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8271661</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,12 +470,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sales Manager, Product- Fraud &amp; Risk</t>
+          <t>Fraud Operations Analyst (CDMX)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dublin or London</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -485,7 +485,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8271661</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8168550</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Supervisor - Trust and Safety Operations</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com/positions/8327049?gh_jid=8327049</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,12 +470,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fraud Operations Analyst (CDMX)</t>
+          <t>Software Engineer, Fraud System Interventions</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>South San Francisco, CA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -485,39 +485,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8168550</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Airbnb</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Supervisor - Trust and Safety Operations</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://careers.airbnb.com/positions/8327049?gh_jid=8327049</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8332718</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Fraud System Interventions</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>South San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8332718</t>
         </is>
       </c>
     </row>
